--- a/data/gravel/Bassi Hog's Back 2025.xlsx
+++ b/data/gravel/Bassi Hog's Back 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8011B33B-CDB2-0B4A-803C-2E0A667D399D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3373A4-5D48-9D47-AB14-6A5BD2B4230D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31160" yWindow="-25220" windowWidth="27360" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13600" yWindow="1340" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="106">
   <si>
     <t>brand</t>
   </si>
@@ -348,6 +348,9 @@
   </si>
   <si>
     <t>Bassi Bikes</t>
+  </si>
+  <si>
+    <t>https://cdn.shoplightspeed.com/shops/633439/files/72666442/image.jpg</t>
   </si>
 </sst>
 </file>
@@ -772,6 +775,11 @@
         <v>88</v>
       </c>
     </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>

--- a/data/gravel/Bassi Hog's Back 2025.xlsx
+++ b/data/gravel/Bassi Hog's Back 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3373A4-5D48-9D47-AB14-6A5BD2B4230D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08023101-1E10-4347-800A-4C7BE19EEC75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13600" yWindow="1340" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -351,6 +351,12 @@
   </si>
   <si>
     <t>https://cdn.shoplightspeed.com/shops/633439/files/72666442/image.jpg</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Montreal, Quebec, Canada</t>
   </si>
 </sst>
 </file>
@@ -728,7 +734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1513,6 +1519,14 @@
         <v>83</v>
       </c>
     </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
